--- a/artfynd/A 27663-2026 artfynd.xlsx
+++ b/artfynd/A 27663-2026 artfynd.xlsx
@@ -1812,11 +1812,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>

--- a/artfynd/A 27663-2026 artfynd.xlsx
+++ b/artfynd/A 27663-2026 artfynd.xlsx
@@ -1786,7 +1786,7 @@
         <v>135449896</v>
       </c>
       <c r="B11" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
